--- a/Template.xlsx
+++ b/Template.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ekm1/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BD42911-05F1-DB49-9B5E-223FDF259688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B064F132-4732-C34F-8388-D5F0B5014719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="860" yWindow="1760" windowWidth="34740" windowHeight="19680" xr2:uid="{63139DA3-2AAE-014D-AF2B-8E259CF4D64C}"/>
   </bookViews>
   <sheets>
-    <sheet name="MSci" sheetId="1" r:id="rId1"/>
+    <sheet name="COURSE NAME" sheetId="1" r:id="rId1"/>
     <sheet name="KEYS" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="41">
   <si>
     <t>Module</t>
   </si>
@@ -145,18 +145,6 @@
     <t>Marshgate</t>
   </si>
   <si>
-    <t>BARC0140 - Making Architecture</t>
-  </si>
-  <si>
-    <t>BARC0146 - Skills Portfolio</t>
-  </si>
-  <si>
-    <t>BARC0142 - 	Sample Building</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BARC0145 - 	History and Theory </t>
-  </si>
-  <si>
     <t>ALL</t>
   </si>
   <si>
@@ -166,12 +154,6 @@
     <t>EC?</t>
   </si>
   <si>
-    <t>BARC0144 - Environmental Concepts and Tools</t>
-  </si>
-  <si>
-    <t>BARC0143 - Structural Concepts and Tools</t>
-  </si>
-  <si>
     <t>Site</t>
   </si>
   <si>
@@ -179,6 +161,9 @@
   </si>
   <si>
     <t>Status</t>
+  </si>
+  <si>
+    <t>Module Code - Module Name</t>
   </si>
 </sst>
 </file>
@@ -296,7 +281,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -381,24 +366,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -782,7 +750,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>9</v>
@@ -831,7 +799,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B3" s="4">
         <v>1</v>
@@ -849,7 +817,7 @@
         <v>100</v>
       </c>
       <c r="G3" s="6">
-        <f t="shared" ref="G3:G54" si="0">ROUNDUP(E3*F3%, 0)</f>
+        <f t="shared" ref="G3:G15" si="0">ROUNDUP(E3*F3%, 0)</f>
         <v>60</v>
       </c>
       <c r="H3" s="16">
@@ -868,7 +836,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B4" s="4">
         <v>1</v>
@@ -904,8 +872,8 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
-        <v>35</v>
+      <c r="A5" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="B5" s="4">
         <v>1</v>
@@ -945,7 +913,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B6" s="4">
         <v>2</v>
@@ -980,8 +948,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
-        <v>34</v>
+      <c r="A7" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="B7" s="4">
         <v>2</v>
@@ -1016,8 +984,8 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
-        <v>36</v>
+      <c r="A8" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="B8" s="4">
         <v>3</v>
@@ -1052,8 +1020,8 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
-        <v>36</v>
+      <c r="A9" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="B9" s="4">
         <v>3</v>
@@ -1089,13 +1057,13 @@
     </row>
     <row r="10" spans="1:13" s="18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="23" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B10" s="18">
         <v>1</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D10" s="19">
         <v>2</v>
@@ -1125,14 +1093,14 @@
       </c>
     </row>
     <row r="11" spans="1:13" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="18" t="s">
-        <v>35</v>
+      <c r="A11" s="23" t="s">
+        <v>40</v>
       </c>
       <c r="B11" s="18">
         <v>1</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D11" s="19">
         <v>2</v>
@@ -1163,13 +1131,13 @@
     </row>
     <row r="12" spans="1:13" s="18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="23" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B12" s="18">
         <v>2</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D12" s="19">
         <v>2</v>
@@ -1200,13 +1168,13 @@
     </row>
     <row r="13" spans="1:13" s="18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="23" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B13" s="18">
         <v>2</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D13" s="19">
         <v>2</v>
@@ -1237,13 +1205,13 @@
     </row>
     <row r="14" spans="1:13" s="18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B14" s="18">
         <v>3</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D14" s="19">
         <v>1</v>
@@ -1274,13 +1242,13 @@
     </row>
     <row r="15" spans="1:13" s="18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B15" s="18">
         <v>3</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D15" s="19">
         <v>1</v>
@@ -1309,614 +1277,569 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:13" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="31"/>
-    </row>
-    <row r="17" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="31"/>
-    </row>
-    <row r="18" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="34"/>
-      <c r="L18" s="31"/>
-    </row>
-    <row r="19" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="34"/>
-      <c r="L19" s="31"/>
-    </row>
-    <row r="20" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="31"/>
-    </row>
-    <row r="21" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="31"/>
-    </row>
-    <row r="22" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="31"/>
-    </row>
-    <row r="23" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="36"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="34"/>
-      <c r="L23" s="31"/>
-    </row>
-    <row r="24" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="34"/>
-      <c r="L24" s="31"/>
-    </row>
-    <row r="25" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="34"/>
-      <c r="L25" s="31"/>
-    </row>
-    <row r="26" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="34"/>
-      <c r="L26" s="31"/>
-    </row>
-    <row r="27" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C27" s="31"/>
-      <c r="D27" s="31"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="35"/>
-      <c r="K27" s="34"/>
-      <c r="L27" s="31"/>
-    </row>
-    <row r="28" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="32"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="31"/>
-    </row>
-    <row r="29" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="34"/>
-      <c r="L29" s="31"/>
-    </row>
-    <row r="30" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="32"/>
-      <c r="J30" s="35"/>
-      <c r="K30" s="34"/>
-      <c r="L30" s="31"/>
-    </row>
-    <row r="31" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="35"/>
-      <c r="K31" s="34"/>
-      <c r="L31" s="31"/>
-    </row>
-    <row r="32" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="35"/>
-      <c r="K32" s="34"/>
-      <c r="L32" s="31"/>
-    </row>
-    <row r="33" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="36"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="33"/>
-      <c r="K33" s="34"/>
-      <c r="L33" s="31"/>
-    </row>
-    <row r="34" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="36"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="32"/>
-      <c r="J34" s="33"/>
-      <c r="K34" s="34"/>
-      <c r="L34" s="31"/>
-    </row>
-    <row r="35" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="37"/>
-      <c r="I35" s="37"/>
-      <c r="J35" s="33"/>
-      <c r="K35" s="34"/>
-      <c r="L35" s="31"/>
-    </row>
-    <row r="36" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="36"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="37"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="34"/>
-      <c r="L36" s="31"/>
-    </row>
-    <row r="37" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="36"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="32"/>
-      <c r="I37" s="32"/>
-      <c r="J37" s="33"/>
-      <c r="K37" s="34"/>
-      <c r="L37" s="31"/>
-    </row>
-    <row r="38" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="36"/>
-      <c r="C38" s="31"/>
-      <c r="D38" s="31"/>
-      <c r="G38" s="31"/>
-      <c r="H38" s="32"/>
-      <c r="I38" s="32"/>
-      <c r="J38" s="33"/>
-      <c r="K38" s="34"/>
-      <c r="L38" s="31"/>
-    </row>
-    <row r="39" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="32"/>
-      <c r="I39" s="32"/>
-      <c r="J39" s="33"/>
-      <c r="K39" s="34"/>
-      <c r="L39" s="31"/>
-    </row>
-    <row r="40" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="32"/>
-      <c r="I40" s="32"/>
-      <c r="J40" s="33"/>
-      <c r="K40" s="34"/>
-      <c r="L40" s="31"/>
-    </row>
-    <row r="41" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
-      <c r="G41" s="31"/>
-      <c r="H41" s="32"/>
-      <c r="I41" s="32"/>
-      <c r="J41" s="33"/>
-      <c r="K41" s="34"/>
-      <c r="L41" s="31"/>
-    </row>
-    <row r="42" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C42" s="31"/>
-      <c r="D42" s="31"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="32"/>
-      <c r="I42" s="32"/>
-      <c r="J42" s="33"/>
-      <c r="K42" s="34"/>
-      <c r="L42" s="31"/>
-    </row>
-    <row r="43" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C43" s="31"/>
-      <c r="D43" s="31"/>
-      <c r="G43" s="31"/>
-      <c r="H43" s="32"/>
-      <c r="I43" s="32"/>
-      <c r="J43" s="35"/>
-      <c r="K43" s="34"/>
-      <c r="L43" s="31"/>
-    </row>
-    <row r="44" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C44" s="31"/>
-      <c r="D44" s="31"/>
-      <c r="G44" s="31"/>
-      <c r="H44" s="32"/>
-      <c r="I44" s="32"/>
-      <c r="J44" s="33"/>
-      <c r="K44" s="34"/>
-      <c r="L44" s="31"/>
-    </row>
-    <row r="45" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
-      <c r="G45" s="31"/>
-      <c r="H45" s="32"/>
-      <c r="I45" s="32"/>
-      <c r="J45" s="33"/>
-      <c r="K45" s="34"/>
-      <c r="L45" s="31"/>
-    </row>
-    <row r="46" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C46" s="31"/>
-      <c r="D46" s="31"/>
-      <c r="G46" s="31"/>
-      <c r="H46" s="32"/>
-      <c r="I46" s="32"/>
-      <c r="J46" s="35"/>
-      <c r="K46" s="34"/>
-      <c r="L46" s="31"/>
-    </row>
-    <row r="47" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="G47" s="31"/>
-      <c r="H47" s="32"/>
-      <c r="I47" s="32"/>
-      <c r="J47" s="33"/>
-      <c r="K47" s="34"/>
-      <c r="L47" s="31"/>
-    </row>
-    <row r="48" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C48" s="31"/>
-      <c r="D48" s="31"/>
-      <c r="G48" s="31"/>
-      <c r="H48" s="37"/>
-      <c r="I48" s="37"/>
-      <c r="J48" s="35"/>
-      <c r="K48" s="34"/>
-      <c r="L48" s="31"/>
-    </row>
-    <row r="49" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C49" s="31"/>
-      <c r="D49" s="31"/>
-      <c r="G49" s="31"/>
-      <c r="H49" s="37"/>
-      <c r="I49" s="37"/>
-      <c r="J49" s="35"/>
-      <c r="K49" s="34"/>
-      <c r="L49" s="31"/>
-    </row>
-    <row r="50" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C50" s="31"/>
-      <c r="D50" s="31"/>
-      <c r="G50" s="31"/>
-      <c r="H50" s="32"/>
-      <c r="I50" s="32"/>
-      <c r="J50" s="33"/>
-      <c r="K50" s="34"/>
-      <c r="L50" s="31"/>
-    </row>
-    <row r="51" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="36"/>
-      <c r="C51" s="31"/>
-      <c r="D51" s="31"/>
-      <c r="G51" s="31"/>
-      <c r="H51" s="32"/>
-      <c r="I51" s="32"/>
-      <c r="J51" s="33"/>
-      <c r="K51" s="34"/>
-      <c r="L51" s="31"/>
-    </row>
-    <row r="52" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C52" s="31"/>
-      <c r="D52" s="31"/>
-      <c r="G52" s="31"/>
-      <c r="H52" s="37"/>
-      <c r="I52" s="37"/>
-      <c r="J52" s="33"/>
-      <c r="K52" s="34"/>
-      <c r="L52" s="31"/>
-    </row>
-    <row r="53" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="36"/>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31"/>
-      <c r="G53" s="31"/>
-      <c r="H53" s="32"/>
-      <c r="I53" s="32"/>
-      <c r="J53" s="33"/>
-      <c r="K53" s="34"/>
-      <c r="L53" s="31"/>
-    </row>
-    <row r="54" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="36"/>
-      <c r="C54" s="31"/>
-      <c r="D54" s="31"/>
-      <c r="G54" s="31"/>
-      <c r="H54" s="32"/>
-      <c r="I54" s="32"/>
-      <c r="J54" s="33"/>
-      <c r="K54" s="34"/>
-      <c r="L54" s="31"/>
-    </row>
-    <row r="55" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C55" s="31"/>
-      <c r="D55" s="31"/>
-      <c r="G55" s="31"/>
-      <c r="H55" s="32"/>
-      <c r="I55" s="32"/>
-      <c r="J55" s="33"/>
-      <c r="K55" s="34"/>
-      <c r="L55" s="31"/>
-    </row>
-    <row r="56" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C56" s="31"/>
-      <c r="D56" s="31"/>
-      <c r="G56" s="31"/>
-      <c r="H56" s="32"/>
-      <c r="I56" s="32"/>
-      <c r="J56" s="33"/>
-      <c r="K56" s="34"/>
-      <c r="L56" s="31"/>
-    </row>
-    <row r="57" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C57" s="31"/>
-      <c r="D57" s="31"/>
-      <c r="G57" s="31"/>
-      <c r="H57" s="32"/>
-      <c r="I57" s="32"/>
-      <c r="J57" s="35"/>
-      <c r="K57" s="34"/>
-      <c r="L57" s="31"/>
-    </row>
-    <row r="58" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C58" s="31"/>
-      <c r="D58" s="31"/>
-      <c r="G58" s="31"/>
-      <c r="H58" s="32"/>
-      <c r="I58" s="32"/>
-      <c r="J58" s="33"/>
-      <c r="K58" s="34"/>
-      <c r="L58" s="31"/>
-    </row>
-    <row r="59" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C59" s="31"/>
-      <c r="D59" s="31"/>
-      <c r="G59" s="31"/>
-      <c r="H59" s="37"/>
-      <c r="I59" s="37"/>
-      <c r="J59" s="35"/>
-      <c r="K59" s="34"/>
-      <c r="L59" s="31"/>
-    </row>
-    <row r="60" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C60" s="31"/>
-      <c r="D60" s="31"/>
-      <c r="G60" s="31"/>
-      <c r="H60" s="37"/>
-      <c r="I60" s="37"/>
-      <c r="J60" s="35"/>
-      <c r="K60" s="34"/>
-      <c r="L60" s="31"/>
-    </row>
-    <row r="61" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C61" s="31"/>
-      <c r="D61" s="31"/>
-      <c r="G61" s="31"/>
-      <c r="H61" s="32"/>
-      <c r="I61" s="32"/>
-      <c r="J61" s="33"/>
-      <c r="K61" s="34"/>
-      <c r="L61" s="31"/>
-    </row>
-    <row r="62" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C62" s="31"/>
-      <c r="D62" s="31"/>
-      <c r="G62" s="31"/>
-      <c r="H62" s="32"/>
-      <c r="I62" s="32"/>
-      <c r="J62" s="33"/>
-      <c r="K62" s="34"/>
-      <c r="L62" s="31"/>
-    </row>
-    <row r="63" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C63" s="31"/>
-      <c r="D63" s="31"/>
-      <c r="G63" s="31"/>
-      <c r="H63" s="32"/>
-      <c r="I63" s="32"/>
-      <c r="J63" s="33"/>
-      <c r="K63" s="34"/>
-      <c r="L63" s="31"/>
-    </row>
-    <row r="64" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C64" s="31"/>
-      <c r="D64" s="31"/>
-      <c r="G64" s="31"/>
-      <c r="H64" s="32"/>
-      <c r="I64" s="32"/>
-      <c r="J64" s="35"/>
-      <c r="K64" s="34"/>
-      <c r="L64" s="31"/>
-    </row>
-    <row r="65" spans="3:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C65" s="31"/>
-      <c r="D65" s="31"/>
-      <c r="G65" s="31"/>
-      <c r="H65" s="32"/>
-      <c r="I65" s="32"/>
-      <c r="J65" s="33"/>
-      <c r="K65" s="34"/>
-      <c r="L65" s="31"/>
-    </row>
-    <row r="66" spans="3:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C66" s="31"/>
-      <c r="D66" s="31"/>
-      <c r="G66" s="31"/>
-      <c r="H66" s="37"/>
-      <c r="I66" s="37"/>
-      <c r="J66" s="35"/>
-      <c r="K66" s="34"/>
-      <c r="L66" s="31"/>
-    </row>
-    <row r="67" spans="3:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C67" s="31"/>
-      <c r="D67" s="31"/>
-      <c r="G67" s="31"/>
-      <c r="H67" s="37"/>
-      <c r="I67" s="37"/>
-      <c r="J67" s="35"/>
-      <c r="K67" s="34"/>
-      <c r="L67" s="31"/>
-    </row>
-    <row r="68" spans="3:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C68" s="31"/>
-      <c r="D68" s="31"/>
-      <c r="G68" s="31"/>
-      <c r="H68" s="32"/>
-      <c r="I68" s="32"/>
-      <c r="J68" s="33"/>
-      <c r="K68" s="34"/>
-      <c r="L68" s="31"/>
-    </row>
-    <row r="69" spans="3:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C69" s="31"/>
-      <c r="D69" s="31"/>
-      <c r="G69" s="31"/>
-      <c r="H69" s="32"/>
-      <c r="I69" s="32"/>
-      <c r="J69" s="33"/>
-      <c r="K69" s="34"/>
-      <c r="L69" s="31"/>
-    </row>
-    <row r="70" spans="3:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C70" s="31"/>
-      <c r="D70" s="31"/>
-      <c r="G70" s="31"/>
-      <c r="H70" s="32"/>
-      <c r="I70" s="32"/>
-      <c r="J70" s="33"/>
-      <c r="K70" s="34"/>
-      <c r="L70" s="31"/>
-    </row>
-    <row r="71" spans="3:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C71" s="31"/>
-      <c r="D71" s="31"/>
-      <c r="G71" s="31"/>
-      <c r="H71" s="32"/>
-      <c r="I71" s="32"/>
-      <c r="J71" s="33"/>
-      <c r="K71" s="34"/>
-      <c r="L71" s="31"/>
-    </row>
-    <row r="72" spans="3:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C72" s="31"/>
-      <c r="D72" s="31"/>
-      <c r="G72" s="31"/>
-      <c r="H72" s="32"/>
-      <c r="I72" s="32"/>
-      <c r="J72" s="33"/>
-      <c r="K72" s="34"/>
-      <c r="L72" s="31"/>
-    </row>
-    <row r="73" spans="3:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C73" s="31"/>
-      <c r="D73" s="31"/>
-      <c r="G73" s="31"/>
-      <c r="H73" s="32"/>
-      <c r="I73" s="32"/>
-      <c r="J73" s="33"/>
-      <c r="K73" s="34"/>
-      <c r="L73" s="31"/>
-    </row>
-    <row r="74" spans="3:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C74" s="31"/>
-      <c r="D74" s="31"/>
-      <c r="G74" s="31"/>
-      <c r="H74" s="32"/>
-      <c r="I74" s="32"/>
-      <c r="J74" s="33"/>
-      <c r="K74" s="34"/>
-      <c r="L74" s="31"/>
-    </row>
-    <row r="75" spans="3:12" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C75" s="31"/>
-      <c r="D75" s="31"/>
-      <c r="G75" s="31"/>
-      <c r="H75" s="32"/>
-      <c r="I75" s="32"/>
-      <c r="J75" s="33"/>
-      <c r="K75" s="34"/>
-      <c r="L75" s="31"/>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="6"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="6"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="6"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="6"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="6"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="6"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="6"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23" s="4"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="6"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="6"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="6"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="6"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="25"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="6"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="6"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="6"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="25"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="6"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="6"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="25"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="6"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A33" s="4"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="6"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A34" s="4"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="6"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="6"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A36" s="4"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="17"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="6"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A37" s="4"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="6"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A38" s="4"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="6"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="6"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="6"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="6"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="6"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="25"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="6"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="6"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="17"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="6"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="25"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="6"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="17"/>
+      <c r="I47" s="17"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="6"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="30"/>
+      <c r="I48" s="30"/>
+      <c r="J48" s="25"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="6"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="25"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="6"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="17"/>
+      <c r="I50" s="17"/>
+      <c r="K50" s="11"/>
+      <c r="L50" s="6"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A51" s="4"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="17"/>
+      <c r="I51" s="17"/>
+      <c r="K51" s="11"/>
+      <c r="L51" s="6"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
+      <c r="K52" s="11"/>
+      <c r="L52" s="6"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A53" s="4"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="17"/>
+      <c r="I53" s="17"/>
+      <c r="K53" s="11"/>
+      <c r="L53" s="6"/>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A54" s="4"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="17"/>
+      <c r="I54" s="17"/>
+      <c r="K54" s="11"/>
+      <c r="L54" s="6"/>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="17"/>
+      <c r="I55" s="17"/>
+      <c r="K55" s="11"/>
+      <c r="L55" s="6"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="17"/>
+      <c r="I56" s="17"/>
+      <c r="K56" s="11"/>
+      <c r="L56" s="6"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="17"/>
+      <c r="I57" s="17"/>
+      <c r="J57" s="25"/>
+      <c r="K57" s="11"/>
+      <c r="L57" s="6"/>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="17"/>
+      <c r="I58" s="17"/>
+      <c r="K58" s="11"/>
+      <c r="L58" s="6"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="30"/>
+      <c r="I59" s="30"/>
+      <c r="J59" s="25"/>
+      <c r="K59" s="11"/>
+      <c r="L59" s="6"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="30"/>
+      <c r="I60" s="30"/>
+      <c r="J60" s="25"/>
+      <c r="K60" s="11"/>
+      <c r="L60" s="6"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="17"/>
+      <c r="I61" s="17"/>
+      <c r="K61" s="11"/>
+      <c r="L61" s="6"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="17"/>
+      <c r="I62" s="17"/>
+      <c r="K62" s="11"/>
+      <c r="L62" s="6"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="17"/>
+      <c r="I63" s="17"/>
+      <c r="K63" s="11"/>
+      <c r="L63" s="6"/>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C64" s="6"/>
+      <c r="D64" s="6"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="17"/>
+      <c r="I64" s="17"/>
+      <c r="J64" s="25"/>
+      <c r="K64" s="11"/>
+      <c r="L64" s="6"/>
+    </row>
+    <row r="65" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="17"/>
+      <c r="I65" s="17"/>
+      <c r="K65" s="11"/>
+      <c r="L65" s="6"/>
+    </row>
+    <row r="66" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="30"/>
+      <c r="I66" s="30"/>
+      <c r="J66" s="25"/>
+      <c r="K66" s="11"/>
+      <c r="L66" s="6"/>
+    </row>
+    <row r="67" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="30"/>
+      <c r="I67" s="30"/>
+      <c r="J67" s="25"/>
+      <c r="K67" s="11"/>
+      <c r="L67" s="6"/>
+    </row>
+    <row r="68" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C68" s="6"/>
+      <c r="D68" s="6"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="17"/>
+      <c r="I68" s="17"/>
+      <c r="K68" s="11"/>
+      <c r="L68" s="6"/>
+    </row>
+    <row r="69" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="17"/>
+      <c r="I69" s="17"/>
+      <c r="K69" s="11"/>
+      <c r="L69" s="6"/>
+    </row>
+    <row r="70" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="17"/>
+      <c r="I70" s="17"/>
+      <c r="K70" s="11"/>
+      <c r="L70" s="6"/>
+    </row>
+    <row r="71" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="17"/>
+      <c r="I71" s="17"/>
+      <c r="K71" s="11"/>
+      <c r="L71" s="6"/>
+    </row>
+    <row r="72" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="17"/>
+      <c r="I72" s="17"/>
+      <c r="K72" s="11"/>
+      <c r="L72" s="6"/>
+    </row>
+    <row r="73" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="17"/>
+      <c r="I73" s="17"/>
+      <c r="K73" s="11"/>
+      <c r="L73" s="6"/>
+    </row>
+    <row r="74" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="17"/>
+      <c r="I74" s="17"/>
+      <c r="K74" s="11"/>
+      <c r="L74" s="6"/>
+    </row>
+    <row r="75" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="17"/>
+      <c r="I75" s="17"/>
+      <c r="K75" s="11"/>
+      <c r="L75" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2005,12 +1928,12 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B9" s="26" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="29" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -2040,7 +1963,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="29" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -2065,7 +1988,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="29" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
